--- a/esyluban/examples/dev/DataTables/test/test_stream.xlsx
+++ b/esyluban/examples/dev/DataTables/test/test_stream.xlsx
@@ -2156,8 +2156,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="M1:N1"/>
     <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
